--- a/diseases/d097/2020-2025.xlsx
+++ b/diseases/d097/2020-2025.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1465,6 +1475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1613,6 +1628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1761,6 +1781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1909,6 +1934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2057,6 +2087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2205,6 +2240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2353,6 +2393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2501,6 +2546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2649,6 +2699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2797,6 +2852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2945,6 +3005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3158,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3241,6 +3311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3389,6 +3464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3537,6 +3617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3685,6 +3770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3833,6 +3923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3981,6 +4076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4129,6 +4229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4277,6 +4382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4425,6 +4535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4573,6 +4688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4721,6 +4841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4869,6 +4994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5017,6 +5147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5165,6 +5300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5313,6 +5453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5461,6 +5606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5609,6 +5759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5757,6 +5912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5905,6 +6065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6053,6 +6218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6201,6 +6371,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6349,6 +6524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6497,6 +6677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6645,6 +6830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6793,6 +6983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6941,6 +7136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7089,6 +7289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7237,6 +7442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7385,6 +7595,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7926,6 +8141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8074,6 +8294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8222,6 +8447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8370,6 +8600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8518,6 +8753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8666,6 +8906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8814,6 +9059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8962,6 +9212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9110,6 +9365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9258,6 +9518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9406,6 +9671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9554,6 +9824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9702,6 +9977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9850,6 +10130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9998,6 +10283,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10146,6 +10436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10294,6 +10589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10442,6 +10742,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10590,6 +10895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10738,6 +11048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10886,6 +11201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11034,6 +11354,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11182,6 +11507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11330,6 +11660,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11478,6 +11813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11626,6 +11966,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11774,6 +12119,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11922,6 +12272,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12070,6 +12425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12218,6 +12578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12366,6 +12731,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12514,6 +12884,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12662,6 +13037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12810,6 +13190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12958,6 +13343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13106,6 +13496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13254,6 +13649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13795,6 +14195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13943,6 +14348,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14091,6 +14501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14239,6 +14654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14387,6 +14807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14535,6 +14960,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14683,6 +15113,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14831,6 +15266,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14979,6 +15419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15127,6 +15572,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15275,6 +15725,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15423,6 +15878,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15571,6 +16031,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15719,6 +16184,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15867,6 +16337,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16015,6 +16490,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16163,6 +16643,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16311,6 +16796,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16459,6 +16949,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16607,6 +17102,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16755,6 +17255,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16903,6 +17408,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17051,6 +17561,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17199,6 +17714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17347,6 +17867,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17495,6 +18020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17643,6 +18173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17791,6 +18326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17939,6 +18479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18087,6 +18632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18235,6 +18785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18383,6 +18938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18531,6 +19091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18679,6 +19244,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18827,6 +19397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18975,6 +19550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19123,6 +19703,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19271,6 +19856,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19419,6 +20009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19567,6 +20162,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19715,6 +20315,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19863,6 +20468,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20011,6 +20621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20159,6 +20774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20307,6 +20927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20455,6 +21080,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20603,6 +21233,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20751,6 +21386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20899,6 +21539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21047,6 +21692,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21195,6 +21845,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21343,6 +21998,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21491,6 +22151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22032,6 +22697,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22180,6 +22850,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22328,6 +23003,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22476,6 +23156,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22624,6 +23309,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22772,6 +23462,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22920,6 +23615,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23068,6 +23768,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23216,6 +23921,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23364,6 +24074,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23512,6 +24227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23660,6 +24380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23808,6 +24533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23956,6 +24686,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24104,6 +24839,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24252,6 +24992,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24400,6 +25145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24548,6 +25298,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24696,6 +25451,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24844,6 +25604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24992,6 +25757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25140,6 +25910,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25288,6 +26063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25436,6 +26216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25584,6 +26369,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25732,6 +26522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25880,6 +26675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26028,6 +26828,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26176,6 +26981,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26324,6 +27134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26472,6 +27287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26620,6 +27440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26768,6 +27593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26916,6 +27746,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27064,6 +27899,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27212,6 +28052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27360,6 +28205,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27508,6 +28358,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27656,6 +28511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27804,6 +28664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27952,6 +28817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28100,6 +28970,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28248,6 +29123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28396,6 +29276,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28544,6 +29429,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28692,6 +29582,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28840,6 +29735,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28988,6 +29888,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29136,6 +30041,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29284,6 +30194,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29432,6 +30347,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29580,6 +30500,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29728,6 +30653,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29876,6 +30806,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30024,6 +30959,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30172,6 +31112,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30320,6 +31265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30468,6 +31418,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30616,6 +31571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30764,6 +31724,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30912,6 +31877,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31060,6 +32030,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31208,6 +32183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31356,6 +32336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31504,6 +32489,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31652,6 +32642,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31800,6 +32795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31948,6 +32948,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32096,6 +33101,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32244,6 +33254,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32392,6 +33407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32540,6 +33560,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32688,6 +33713,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32836,6 +33866,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32984,6 +34019,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33132,6 +34172,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33280,6 +34325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33428,6 +34478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33576,6 +34631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33724,6 +34784,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33872,6 +34937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34020,6 +35090,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34168,6 +35243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34316,6 +35396,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34464,6 +35549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34612,6 +35702,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34760,6 +35855,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34908,6 +36008,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35056,6 +36161,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35204,6 +36314,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35352,6 +36467,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35500,6 +36620,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35648,6 +36773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35796,6 +36926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35944,6 +37079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36092,6 +37232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36240,6 +37385,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36388,6 +37538,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36536,6 +37691,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36684,6 +37844,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36832,6 +37997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36980,6 +38150,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37128,6 +38303,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37276,6 +38456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37424,6 +38609,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37572,6 +38762,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37720,6 +38915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37868,6 +39068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38016,6 +39221,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38164,6 +39374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38312,6 +39527,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38460,6 +39680,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38608,6 +39833,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38756,6 +39986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38904,6 +40139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39052,6 +40292,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39200,6 +40445,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39348,6 +40598,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39496,6 +40751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39644,6 +40904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39792,6 +41057,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39940,6 +41210,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40088,6 +41363,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40236,6 +41516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40384,6 +41669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40532,6 +41822,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40680,6 +41975,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40828,6 +42128,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40976,6 +42281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41124,6 +42434,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41272,6 +42587,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41420,6 +42740,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41568,6 +42893,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41716,6 +43046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41864,6 +43199,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42012,6 +43352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42160,6 +43505,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42308,6 +43658,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42456,6 +43811,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42604,6 +43964,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42752,6 +44117,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42900,6 +44270,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43048,6 +44423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43196,6 +44576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43344,6 +44729,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43492,6 +44882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43640,6 +45035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43788,6 +45188,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43936,6 +45341,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44084,6 +45494,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44232,6 +45647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44380,6 +45800,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44528,6 +45953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44676,6 +46106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44824,6 +46259,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44970,6 +46410,11 @@
       <c r="S298" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">

--- a/diseases/d097/2020-2025.xlsx
+++ b/diseases/d097/2020-2025.xlsx
@@ -14337,9 +14337,6 @@
       <c r="O89" t="n">
         <v>2</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -14949,9 +14946,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -15408,9 +15402,6 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -15714,9 +15705,6 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -15867,9 +15855,6 @@
       <c r="O99" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16020,9 +16005,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -16173,9 +16155,6 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16326,9 +16305,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -16632,9 +16608,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -16785,9 +16758,6 @@
       <c r="O105" t="n">
         <v>2</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16938,9 +16908,6 @@
       <c r="O106" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -17091,9 +17058,6 @@
       <c r="O107" t="n">
         <v>5</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -17244,9 +17208,6 @@
       <c r="O108" t="n">
         <v>3</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.0008783897358191777</v>
       </c>
@@ -17397,9 +17358,6 @@
       <c r="O109" t="n">
         <v>11</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.003220762364670318</v>
       </c>
@@ -17550,9 +17508,6 @@
       <c r="O110" t="n">
         <v>11</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.003220762364670318</v>
       </c>
@@ -17703,9 +17658,6 @@
       <c r="O111" t="n">
         <v>15</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.004391948679095889</v>
       </c>
@@ -17856,9 +17808,6 @@
       <c r="O112" t="n">
         <v>27</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.007905507622372599</v>
       </c>
@@ -18009,9 +17958,6 @@
       <c r="O113" t="n">
         <v>18</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.005270338414915066</v>
       </c>
@@ -18162,9 +18108,6 @@
       <c r="O114" t="n">
         <v>13</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.003806355521883103</v>
       </c>
@@ -18315,9 +18258,6 @@
       <c r="O115" t="n">
         <v>19</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.005563134993521458</v>
       </c>
@@ -18468,9 +18408,6 @@
       <c r="O116" t="n">
         <v>74</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.02166694681687305</v>
       </c>
@@ -18621,9 +18558,6 @@
       <c r="O117" t="n">
         <v>56</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.01639660840195798</v>
       </c>
@@ -18774,9 +18708,6 @@
       <c r="O118" t="n">
         <v>108</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.0316220304894904</v>
       </c>
@@ -18927,9 +18858,6 @@
       <c r="O119" t="n">
         <v>78</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.02283813313129862</v>
       </c>
@@ -19080,9 +19008,6 @@
       <c r="O120" t="n">
         <v>41</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.0120046597228621</v>
       </c>
@@ -19233,9 +19158,6 @@
       <c r="O121" t="n">
         <v>31</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.009076693936798169</v>
       </c>
@@ -19386,9 +19308,6 @@
       <c r="O122" t="n">
         <v>31</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.009076693936798169</v>
       </c>
@@ -19539,9 +19458,6 @@
       <c r="O123" t="n">
         <v>28</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.00819830420097899</v>
       </c>
@@ -19692,9 +19608,6 @@
       <c r="O124" t="n">
         <v>17</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.004977541836308674</v>
       </c>
@@ -19845,9 +19758,6 @@
       <c r="O125" t="n">
         <v>10</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.002927965786063926</v>
       </c>
@@ -19998,9 +19908,6 @@
       <c r="O126" t="n">
         <v>10</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.002927965786063926</v>
       </c>
@@ -20151,9 +20058,6 @@
       <c r="O127" t="n">
         <v>10</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.002927965786063926</v>
       </c>
@@ -20304,9 +20208,6 @@
       <c r="O128" t="n">
         <v>4</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.00117118631442557</v>
       </c>
@@ -20457,9 +20358,6 @@
       <c r="O129" t="n">
         <v>9</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.002635169207457533</v>
       </c>
@@ -20610,9 +20508,6 @@
       <c r="O130" t="n">
         <v>5</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -20763,9 +20658,6 @@
       <c r="O131" t="n">
         <v>6</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.001756779471638355</v>
       </c>
@@ -20916,9 +20808,6 @@
       <c r="O132" t="n">
         <v>12</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.003513558943276711</v>
       </c>
@@ -21069,9 +20958,6 @@
       <c r="O133" t="n">
         <v>12</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.003513558943276711</v>
       </c>
@@ -21222,9 +21108,6 @@
       <c r="O134" t="n">
         <v>9</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.002635169207457533</v>
       </c>
@@ -21375,9 +21258,6 @@
       <c r="O135" t="n">
         <v>3</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.0008783897358191777</v>
       </c>
@@ -21528,9 +21408,6 @@
       <c r="O136" t="n">
         <v>6</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.001756779471638355</v>
       </c>
@@ -21681,9 +21558,6 @@
       <c r="O137" t="n">
         <v>5</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -21834,9 +21708,6 @@
       <c r="O138" t="n">
         <v>2</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -21987,9 +21858,6 @@
       <c r="O139" t="n">
         <v>2</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -22140,9 +22008,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -22839,9 +22704,6 @@
       <c r="O144" t="n">
         <v>4</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -22992,9 +22854,6 @@
       <c r="O145" t="n">
         <v>2</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -23145,9 +23004,6 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -23298,9 +23154,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -23451,9 +23304,6 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -23604,9 +23454,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24216,9 +24063,6 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24369,9 +24213,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24522,9 +24363,6 @@
       <c r="O155" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -24675,9 +24513,6 @@
       <c r="O156" t="n">
         <v>5</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.001455700126472683</v>
       </c>
@@ -24828,9 +24663,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24981,9 +24813,6 @@
       <c r="O158" t="n">
         <v>2</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -25134,9 +24963,6 @@
       <c r="O159" t="n">
         <v>4</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -25287,9 +25113,6 @@
       <c r="O160" t="n">
         <v>13</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.003784820328828975</v>
       </c>
@@ -25440,9 +25263,6 @@
       <c r="O161" t="n">
         <v>12</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.003493680303534439</v>
       </c>
@@ -25593,9 +25413,6 @@
       <c r="O162" t="n">
         <v>11</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.003202540278239902</v>
       </c>
@@ -25746,9 +25563,6 @@
       <c r="O163" t="n">
         <v>14</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.004075960354123511</v>
       </c>
@@ -25899,9 +25713,6 @@
       <c r="O164" t="n">
         <v>30</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.008734200758836096</v>
       </c>
@@ -26052,9 +25863,6 @@
       <c r="O165" t="n">
         <v>35</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.01018990088530878</v>
       </c>
@@ -26205,9 +26013,6 @@
       <c r="O166" t="n">
         <v>36</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.01048104091060332</v>
       </c>
@@ -26358,9 +26163,6 @@
       <c r="O167" t="n">
         <v>25</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.007278500632363413</v>
       </c>
@@ -26511,9 +26313,6 @@
       <c r="O168" t="n">
         <v>42</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.01222788106237054</v>
       </c>
@@ -26664,9 +26463,6 @@
       <c r="O169" t="n">
         <v>68</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.01979752172002848</v>
       </c>
@@ -26817,9 +26613,6 @@
       <c r="O170" t="n">
         <v>104</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.0302785626306318</v>
       </c>
@@ -26970,9 +26763,6 @@
       <c r="O171" t="n">
         <v>119</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.03464566301004985</v>
       </c>
@@ -27123,9 +26913,6 @@
       <c r="O172" t="n">
         <v>92</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.02678488232709736</v>
       </c>
@@ -27276,9 +27063,6 @@
       <c r="O173" t="n">
         <v>73</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.02125322184650117</v>
       </c>
@@ -27429,9 +27213,6 @@
       <c r="O174" t="n">
         <v>59</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.01717726149237766</v>
       </c>
@@ -27582,9 +27363,6 @@
       <c r="O175" t="n">
         <v>57</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01659498144178858</v>
       </c>
@@ -27735,9 +27513,6 @@
       <c r="O176" t="n">
         <v>74</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.0215443618717957</v>
       </c>
@@ -27888,9 +27663,6 @@
       <c r="O177" t="n">
         <v>29</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.00844306073354156</v>
       </c>
@@ -28041,9 +27813,6 @@
       <c r="O178" t="n">
         <v>13</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.003784820328828975</v>
       </c>
@@ -28194,9 +27963,6 @@
       <c r="O179" t="n">
         <v>11</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.003202540278239902</v>
       </c>
@@ -28347,9 +28113,6 @@
       <c r="O180" t="n">
         <v>5</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.001455700126472683</v>
       </c>
@@ -28500,9 +28263,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -28653,9 +28413,6 @@
       <c r="O182" t="n">
         <v>2</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -28806,9 +28563,6 @@
       <c r="O183" t="n">
         <v>6</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.001746840151767219</v>
       </c>
@@ -28959,9 +28713,6 @@
       <c r="O184" t="n">
         <v>5</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.001455700126472683</v>
       </c>
@@ -29265,9 +29016,6 @@
       <c r="O186" t="n">
         <v>5</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.001455700126472683</v>
       </c>
@@ -29418,9 +29166,6 @@
       <c r="O187" t="n">
         <v>1</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -29571,9 +29316,6 @@
       <c r="O188" t="n">
         <v>3</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -29877,9 +29619,6 @@
       <c r="O190" t="n">
         <v>3</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -30030,9 +29769,6 @@
       <c r="O191" t="n">
         <v>2</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -30183,9 +29919,6 @@
       <c r="O192" t="n">
         <v>5</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.001455700126472683</v>
       </c>
@@ -30336,9 +30069,6 @@
       <c r="O193" t="n">
         <v>2</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -30795,9 +30525,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -30948,9 +30675,6 @@
       <c r="O197" t="n">
         <v>2</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -31101,9 +30825,6 @@
       <c r="O198" t="n">
         <v>4</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -31254,9 +30975,6 @@
       <c r="O199" t="n">
         <v>2</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -31407,9 +31125,6 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -31866,9 +31581,6 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -32019,9 +31731,6 @@
       <c r="O204" t="n">
         <v>2</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -32172,9 +31881,6 @@
       <c r="O205" t="n">
         <v>2</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -32325,9 +32031,6 @@
       <c r="O206" t="n">
         <v>3</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -32478,9 +32181,6 @@
       <c r="O207" t="n">
         <v>3</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -32631,9 +32331,6 @@
       <c r="O208" t="n">
         <v>2</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -32784,9 +32481,6 @@
       <c r="O209" t="n">
         <v>2</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -32937,9 +32631,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -33090,9 +32781,6 @@
       <c r="O211" t="n">
         <v>4</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -33243,9 +32931,6 @@
       <c r="O212" t="n">
         <v>5</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -33396,9 +33081,6 @@
       <c r="O213" t="n">
         <v>3</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -33549,9 +33231,6 @@
       <c r="O214" t="n">
         <v>2</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -33702,9 +33381,6 @@
       <c r="O215" t="n">
         <v>5</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -33855,9 +33531,6 @@
       <c r="O216" t="n">
         <v>5</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -34008,9 +33681,6 @@
       <c r="O217" t="n">
         <v>12</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.00347396552768374</v>
       </c>
@@ -34161,9 +33831,6 @@
       <c r="O218" t="n">
         <v>18</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.005210948291525611</v>
       </c>
@@ -34314,9 +33981,6 @@
       <c r="O219" t="n">
         <v>35</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.01013239945574424</v>
       </c>
@@ -34467,9 +34131,6 @@
       <c r="O220" t="n">
         <v>42</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.01215887934689309</v>
       </c>
@@ -34620,9 +34281,6 @@
       <c r="O221" t="n">
         <v>67</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.01939630752956755</v>
       </c>
@@ -34773,9 +34431,6 @@
       <c r="O222" t="n">
         <v>73</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.02113329029340942</v>
       </c>
@@ -34926,9 +34581,6 @@
       <c r="O223" t="n">
         <v>93</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.02692323283954898</v>
       </c>
@@ -35079,9 +34731,6 @@
       <c r="O224" t="n">
         <v>148</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.0428455748414328</v>
       </c>
@@ -35232,9 +34881,6 @@
       <c r="O225" t="n">
         <v>167</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.04834602026026538</v>
       </c>
@@ -35385,9 +35031,6 @@
       <c r="O226" t="n">
         <v>119</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.03445015814953042</v>
       </c>
@@ -35538,9 +35181,6 @@
       <c r="O227" t="n">
         <v>79</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.02287027305725129</v>
       </c>
@@ -35691,9 +35331,6 @@
       <c r="O228" t="n">
         <v>68</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.01968580465687453</v>
       </c>
@@ -35844,9 +35481,6 @@
       <c r="O229" t="n">
         <v>50</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.01447485636534892</v>
       </c>
@@ -35997,9 +35631,6 @@
       <c r="O230" t="n">
         <v>23</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.006658433928060503</v>
       </c>
@@ -36150,9 +35781,6 @@
       <c r="O231" t="n">
         <v>27</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.007816422437288416</v>
       </c>
@@ -36303,9 +35931,6 @@
       <c r="O232" t="n">
         <v>25</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.007237428182674459</v>
       </c>
@@ -36456,9 +36081,6 @@
       <c r="O233" t="n">
         <v>6</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.00173698276384187</v>
       </c>
@@ -36609,9 +36231,6 @@
       <c r="O234" t="n">
         <v>13</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.003763462654990719</v>
       </c>
@@ -36762,9 +36381,6 @@
       <c r="O235" t="n">
         <v>6</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.00173698276384187</v>
       </c>
@@ -36915,9 +36531,6 @@
       <c r="O236" t="n">
         <v>2</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -37068,9 +36681,6 @@
       <c r="O237" t="n">
         <v>3</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -37221,9 +36831,6 @@
       <c r="O238" t="n">
         <v>24</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.006947931055367481</v>
       </c>
@@ -37374,9 +36981,6 @@
       <c r="O239" t="n">
         <v>62</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.01794882189303266</v>
       </c>
@@ -37527,9 +37131,6 @@
       <c r="O240" t="n">
         <v>37</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.0107113937103582</v>
       </c>
@@ -37680,9 +37281,6 @@
       <c r="O241" t="n">
         <v>7</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.002026479891148849</v>
       </c>
@@ -37833,9 +37431,6 @@
       <c r="O242" t="n">
         <v>5</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -37986,9 +37581,6 @@
       <c r="O243" t="n">
         <v>5</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -38139,9 +37731,6 @@
       <c r="O244" t="n">
         <v>6</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.00173698276384187</v>
       </c>
@@ -38292,9 +37881,6 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -38445,9 +38031,6 @@
       <c r="O246" t="n">
         <v>1</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -38598,9 +38181,6 @@
       <c r="O247" t="n">
         <v>2</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -38751,9 +38331,6 @@
       <c r="O248" t="n">
         <v>2</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -39057,9 +38634,6 @@
       <c r="O250" t="n">
         <v>2</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -39210,9 +38784,6 @@
       <c r="O251" t="n">
         <v>1</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -39363,9 +38934,6 @@
       <c r="O252" t="n">
         <v>3</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -39516,9 +39084,6 @@
       <c r="O253" t="n">
         <v>2</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -39822,9 +39387,6 @@
       <c r="O255" t="n">
         <v>2</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -39975,9 +39537,6 @@
       <c r="O256" t="n">
         <v>2</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -40128,9 +39687,6 @@
       <c r="O257" t="n">
         <v>7</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.002015688927596835</v>
       </c>
@@ -40281,9 +39837,6 @@
       <c r="O258" t="n">
         <v>3</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -40434,9 +39987,6 @@
       <c r="O259" t="n">
         <v>4</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -40740,9 +40290,6 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -40893,9 +40440,6 @@
       <c r="O262" t="n">
         <v>2</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -41046,9 +40590,6 @@
       <c r="O263" t="n">
         <v>3</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -41199,9 +40740,6 @@
       <c r="O264" t="n">
         <v>4</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -41352,9 +40890,6 @@
       <c r="O265" t="n">
         <v>5</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.001439777805426311</v>
       </c>
@@ -41505,9 +41040,6 @@
       <c r="O266" t="n">
         <v>6</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.001727733366511573</v>
       </c>
@@ -41653,16 +41185,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O267" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q267" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R267" t="n">
-        <v>0.001439777805426311</v>
+        <v>0.001151822244341049</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -41811,9 +41340,6 @@
       <c r="O268" t="n">
         <v>9</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.002591600049767359</v>
       </c>
@@ -41964,9 +41490,6 @@
       <c r="O269" t="n">
         <v>9</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.002591600049767359</v>
       </c>
@@ -42117,9 +41640,6 @@
       <c r="O270" t="n">
         <v>23</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.006622977904961031</v>
       </c>
@@ -42270,9 +41790,6 @@
       <c r="O271" t="n">
         <v>34</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.009790489076898914</v>
       </c>
@@ -42423,9 +41940,6 @@
       <c r="O272" t="n">
         <v>58</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.01670142254294521</v>
       </c>
@@ -42576,9 +42090,6 @@
       <c r="O273" t="n">
         <v>65</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.01871711147054204</v>
       </c>
@@ -42729,9 +42240,6 @@
       <c r="O274" t="n">
         <v>129</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.03714626737999882</v>
       </c>
@@ -42882,9 +42390,6 @@
       <c r="O275" t="n">
         <v>123</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.03541853401348725</v>
       </c>
@@ -43035,9 +42540,6 @@
       <c r="O276" t="n">
         <v>158</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.04549697865147143</v>
       </c>
@@ -43188,9 +42690,6 @@
       <c r="O277" t="n">
         <v>119</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.0342667117691462</v>
       </c>
@@ -43341,9 +42840,6 @@
       <c r="O278" t="n">
         <v>108</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.03109920059720831</v>
       </c>
@@ -43494,9 +42990,6 @@
       <c r="O279" t="n">
         <v>97</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.02793168942527043</v>
       </c>
@@ -43647,9 +43140,6 @@
       <c r="O280" t="n">
         <v>84</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.02418826713116203</v>
       </c>
@@ -43800,9 +43290,6 @@
       <c r="O281" t="n">
         <v>36</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.01036640019906944</v>
       </c>
@@ -43953,9 +43440,6 @@
       <c r="O282" t="n">
         <v>24</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.006910933466046292</v>
       </c>
@@ -44106,9 +43590,6 @@
       <c r="O283" t="n">
         <v>27</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.007774800149302079</v>
       </c>
@@ -44259,9 +43740,6 @@
       <c r="O284" t="n">
         <v>16</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.004607288977364195</v>
       </c>
@@ -44412,9 +43890,6 @@
       <c r="O285" t="n">
         <v>13</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.003743422294108408</v>
       </c>
@@ -44565,9 +44040,6 @@
       <c r="O286" t="n">
         <v>6</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.001727733366511573</v>
       </c>
@@ -44718,9 +44190,6 @@
       <c r="O287" t="n">
         <v>13</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.003743422294108408</v>
       </c>
@@ -44871,9 +44340,6 @@
       <c r="O288" t="n">
         <v>19</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.005471155660619982</v>
       </c>
@@ -45024,9 +44490,6 @@
       <c r="O289" t="n">
         <v>6</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.001727733366511573</v>
       </c>
@@ -45177,9 +44640,6 @@
       <c r="O290" t="n">
         <v>6</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.001727733366511573</v>
       </c>
@@ -45483,9 +44943,6 @@
       <c r="O292" t="n">
         <v>3</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -45636,9 +45093,6 @@
       <c r="O293" t="n">
         <v>5</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.001439777805426311</v>
       </c>
@@ -45789,9 +45243,6 @@
       <c r="O294" t="n">
         <v>4</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -45942,9 +45393,6 @@
       <c r="O295" t="n">
         <v>4</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -46095,9 +45543,6 @@
       <c r="O296" t="n">
         <v>2</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -46248,9 +45693,6 @@
       <c r="O297" t="n">
         <v>3</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -46400,9 +45842,6 @@
       </c>
       <c r="O298" t="n">
         <v>1</v>
-      </c>
-      <c r="Q298" t="n">
-        <v>0</v>
       </c>
       <c r="R298" t="n">
         <v>0.0002879555610852622</v>
@@ -46660,7 +46099,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7428</v>
+        <v>7427</v>
       </c>
     </row>
     <row r="16">
